--- a/HumanFactorsExperiment/实验3/照度测量结果.xlsx
+++ b/HumanFactorsExperiment/实验3/照度测量结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\20230\Desktop\Assignment\HumanFactorsExperiment\实验3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0492F8-53F3-4C10-9973-E86BC3252A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B236ED5-789C-46E3-B4F4-218BDE6A1567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,9 +29,35 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+  <si>
+    <t>监测项目</t>
+  </si>
+  <si>
+    <t>平均实测值</t>
+  </si>
+  <si>
+    <t>空气温度</t>
+  </si>
+  <si>
+    <t>17.13 C</t>
+  </si>
+  <si>
+    <t>相对湿度</t>
+  </si>
+  <si>
+    <t>平均风速</t>
+  </si>
+  <si>
+    <t>0.35 m/s</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,6 +78,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -61,7 +100,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -175,11 +214,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +271,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -232,6 +295,8214 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>自然光照度分布</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surface3DChart>
+        <c:wireframe val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C0B0-4CE0-A664-D2ADE1B23038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C0B0-4CE0-A664-D2ADE1B23038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C0B0-4CE0-A664-D2ADE1B23038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>53</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C0B0-4CE0-A664-D2ADE1B23038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>114</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$6:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>162</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C0B0-4CE0-A664-D2ADE1B23038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$7:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C0B0-4CE0-A664-D2ADE1B23038}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1570212400"/>
+        <c:axId val="1570218160"/>
+        <c:axId val="1441689520"/>
+      </c:surface3DChart>
+      <c:catAx>
+        <c:axId val="1570212400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1570218160"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1570218160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1570212400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1441689520"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1570218160"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>自然光等照度线</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="90"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surfaceChart>
+        <c:wireframe val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F6AB-4C9E-955B-1973777C292E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F6AB-4C9E-955B-1973777C292E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F6AB-4C9E-955B-1973777C292E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>53</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F6AB-4C9E-955B-1973777C292E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>114</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$6:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>162</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-F6AB-4C9E-955B-1973777C292E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>自然光!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>自然光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>自然光!$B$7:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-F6AB-4C9E-955B-1973777C292E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1616756512"/>
+        <c:axId val="1616753152"/>
+        <c:axId val="1616738192"/>
+      </c:surfaceChart>
+      <c:catAx>
+        <c:axId val="1616756512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616753152"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1616753152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616756512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1616738192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616753152"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>混合光照度分布</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surface3DChart>
+        <c:wireframe val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>140</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>138</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-430E-4AEE-AAAE-3C2F596ADD85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>202</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-430E-4AEE-AAAE-3C2F596ADD85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-430E-4AEE-AAAE-3C2F596ADD85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>216</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>289</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>363</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>269</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-430E-4AEE-AAAE-3C2F596ADD85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>309</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$6:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>401</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-430E-4AEE-AAAE-3C2F596ADD85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$7:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="3">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>177</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-430E-4AEE-AAAE-3C2F596ADD85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1570220080"/>
+        <c:axId val="1570223440"/>
+        <c:axId val="1616740992"/>
+      </c:surface3DChart>
+      <c:catAx>
+        <c:axId val="1570220080"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1570223440"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1570223440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1570220080"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1616740992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1570223440"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>混合光等照度线</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="90"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surfaceChart>
+        <c:wireframe val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>140</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>138</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AC23-4C6A-A937-EF66B4F58B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>202</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AC23-4C6A-A937-EF66B4F58B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AC23-4C6A-A937-EF66B4F58B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>216</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>289</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>363</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>269</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-AC23-4C6A-A937-EF66B4F58B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>309</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$6:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>401</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-AC23-4C6A-A937-EF66B4F58B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>混合光!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>混合光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>混合光!$B$7:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="3">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>177</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-AC23-4C6A-A937-EF66B4F58B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1614320944"/>
+        <c:axId val="1614319504"/>
+        <c:axId val="1441686720"/>
+      </c:surfaceChart>
+      <c:catAx>
+        <c:axId val="1614320944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1614319504"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1614319504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1614320944"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1441686720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1614319504"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>人造光照度分布</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surface3DChart>
+        <c:wireframe val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>139</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>181</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D62-4B93-9CC9-8ED77E415CFA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>170</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3D62-4B93-9CC9-8ED77E415CFA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>183</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3D62-4B93-9CC9-8ED77E415CFA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>161</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>192</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3D62-4B93-9CC9-8ED77E415CFA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>178</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$6:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>134</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3D62-4B93-9CC9-8ED77E415CFA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$7:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="3">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>188</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-3D62-4B93-9CC9-8ED77E415CFA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1616759392"/>
+        <c:axId val="1616757472"/>
+        <c:axId val="1616739872"/>
+      </c:surface3DChart>
+      <c:catAx>
+        <c:axId val="1616759392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616757472"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1616757472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616759392"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1616739872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616757472"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>人造光等照度线</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="90"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:surfaceChart>
+        <c:wireframe val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>139</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>181</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7DF4-48EC-9D14-B3FB27D6779F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$3:$P$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>170</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7DF4-48EC-9D14-B3FB27D6779F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$4:$P$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>183</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7DF4-48EC-9D14-B3FB27D6779F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>161</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$5:$P$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>192</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7DF4-48EC-9D14-B3FB27D6779F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>178</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$6:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>134</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7DF4-48EC-9D14-B3FB27D6779F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>人造光!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>人造光!$B$1:$P$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>人造光!$B$7:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="3">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>188</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7DF4-48EC-9D14-B3FB27D6779F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:bandFmts>
+          <c:bandFmt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="8"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="9"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="10"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="11"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="12"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="13"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+          <c:bandFmt>
+            <c:idx val="14"/>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:bandFmt>
+        </c:bandFmts>
+        <c:axId val="1616761312"/>
+        <c:axId val="1616752672"/>
+        <c:axId val="1441687280"/>
+      </c:surfaceChart>
+      <c:catAx>
+        <c:axId val="1616761312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616752672"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1616752672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616761312"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1441687280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1616752672"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C05170B0-B8F9-776B-2518-07051A96D812}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>212725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>692150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>92075</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="图表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B5A691F-46C1-45AA-9CD6-852BDC54BC0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>730250</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FE3BAC9-6BBF-B338-BEE1-DF0BB6D54208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{714A1ED7-BBA5-C77B-DBC8-4B585C0F45B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>73025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA490C36-1485-573F-0447-50D503F0ED3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>793750</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE2AD1A-59D7-4713-6A75-A9AABCB3060C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -822,6 +9093,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1162,12 +9434,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090BB7FC-3040-4BF7-AB35-4F421265169B}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="10.58203125" customWidth="1"/>
@@ -1499,8 +9772,66 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
+    <row r="30" spans="7:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="7:13" ht="15.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G31" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G32" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0.70479999999999998</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G33" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0.70479999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>